--- a/reports/jobs_2026-10-28.xlsx
+++ b/reports/jobs_2026-10-28.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$117</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I114"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Key Takeaways from Tech at Agoda: From Assistants to AI Agents October 27, 2026 /</t>
+          <t>Graduate Machine Learning Engineer - Central Technology</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/blog/tech/key-takeaways-from-tech-at-agoda-from-assistants-to-ai-agents/</t>
+          <t>https://careers.arm.com/job/lund/graduate-machine-learning-engineer-central-technology/33099/102539121824</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -563,17 +563,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Backend Software Engineer - Focus Funds and AI</t>
+          <t>Physical AI Quality Intern</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -581,11 +581,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -593,12 +589,12 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27824</t>
+          <t>https://careers.arm.com/job/cambridge/physical-ai-quality-intern/33099/101898108368</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -610,17 +606,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Graduate ML Software Engineer</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -628,11 +624,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -640,12 +632,12 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27823</t>
+          <t>https://careers.arm.com/job/lund/graduate-ml-software-engineer/33099/102539110752</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -657,12 +649,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Commvault India</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Backend Software Engineer - Identity</t>
+          <t>Software Engineer (C++/Python)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -677,7 +669,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Bangalore, India; Hyderbad, India</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -687,12 +679,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27819</t>
+          <t>https://job-boards.greenhouse.io/commvault/jobs/5441176008</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://boards.greenhouse.io/commvault</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -702,108 +694,104 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Atlassian India</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Backend Software Engineer</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru or Remote</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.atlassian.com/company/careers/details/26676</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Agnikul Cosmos</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Careers Inquiries humancapital@agnikul.in</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>mailto:%20humancapital@agnikul.in</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>https://agnikul.in/careers</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Atlassian India</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Frontend Software Engineer</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.atlassian.com/company/careers/details/26674</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Agoda India</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Chiang Mai 1 available jobs</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 1 available jobs Ok</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>https://careersatagoda.com/location/chiang-mai/</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>https://careersatagoda.com/</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Agnikul Cosmos</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Careers Inquiries humancapital@agnikul.in</t>
+          <t>Dubai 0 available jobs</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -816,7 +804,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 1 available jobs Ok</t>
+        </is>
+      </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -824,12 +816,12 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>mailto:%20humancapital@agnikul.in</t>
+          <t>https://careersatagoda.com/location/dubai/</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://agnikul.in/careers</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -846,7 +838,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Chiang Mai 1 available jobs</t>
+          <t>Mumbai 1 available jobs</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -871,7 +863,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/chiang-mai/</t>
+          <t>https://careersatagoda.com/location/mumbai/</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -893,7 +885,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Dubai 0 available jobs</t>
+          <t>Shanghai 2 available jobs</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -918,7 +910,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/dubai/</t>
+          <t>https://careersatagoda.com/location/shanghai/</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -940,7 +932,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Mumbai 1 available jobs</t>
+          <t>Engineering &amp; Technology</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -953,11 +945,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 1 available jobs Ok</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -965,7 +953,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai/</t>
+          <t>https://careersatagoda.com/department/technology/</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -987,7 +975,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Shanghai 2 available jobs</t>
+          <t>Key Takeaways from Tech at Agoda: From Assistants to AI Agents October 27, 2026 /</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1000,11 +988,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 1 available jobs Ok</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -1012,7 +996,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/shanghai/</t>
+          <t>https://careersatagoda.com/blog/tech/key-takeaways-from-tech-at-agoda-from-assistants-to-ai-agents/</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1034,7 +1018,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Technology</t>
+          <t>How We Cut the Coupling Tax in a Post-Booking API October 20, 2026 /</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1055,7 +1039,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/department/technology/</t>
+          <t>https://careersatagoda.com/blog/tech/how-we-cut-the-coupling-tax-in-a-post-booking-api/</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1077,7 +1061,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>How We Cut the Coupling Tax in a Post-Booking API October 20, 2026 /</t>
+          <t>Mumbai jobs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1090,7 +1074,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai jobs Yokohama jobs</t>
+        </is>
+      </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -1098,7 +1086,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/blog/tech/how-we-cut-the-coupling-tax-in-a-post-booking-api/</t>
+          <t>https://careersatagoda.com/location/mumbai-india/</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1120,12 +1108,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mumbai jobs</t>
+          <t>Backend Developer Jobs</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1133,11 +1121,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai jobs Yokohama jobs</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -1145,7 +1129,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai-india/</t>
+          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1167,12 +1151,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer Jobs</t>
+          <t>Full Stack Developer Jobs</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1188,7 +1172,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
+          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1210,12 +1194,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer Jobs</t>
+          <t>Software Engineer Jobs</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1231,7 +1215,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
+          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1248,17 +1232,17 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Jobs</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1274,12 +1258,12 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
+          <t>https://www.atlassian.com/company/careers/details/27443</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1296,12 +1280,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Development Engineer</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1309,7 +1293,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -1317,7 +1305,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27443</t>
+          <t>https://www.atlassian.com/company/careers/details/26833</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1339,12 +1327,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Application Development Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1364,7 +1352,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26833</t>
+          <t>https://www.atlassian.com/company/careers/details/27794</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1386,12 +1374,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1411,7 +1399,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25561</t>
+          <t>https://www.atlassian.com/company/careers/details/25538</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1433,12 +1421,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>EMEA Field CTO, DX — Engineering Executive Advisor</t>
+          <t>Backend Software Engineer - Focus Funds and AI</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1458,7 +1446,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/24899</t>
+          <t>https://www.atlassian.com/company/careers/details/27824</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1505,7 +1493,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27794</t>
+          <t>https://www.atlassian.com/company/careers/details/27823</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1527,12 +1515,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>AI Researcher, 2027 Graduate U.S.</t>
+          <t>Backend Software Engineer - Identity</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1552,7 +1540,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26246</t>
+          <t>https://www.atlassian.com/company/careers/details/27819</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1574,12 +1562,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1599,7 +1587,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25538</t>
+          <t>https://www.atlassian.com/company/careers/details/26674</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1621,12 +1609,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1646,7 +1634,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25539</t>
+          <t>https://www.atlassian.com/company/careers/details/25561</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1668,12 +1656,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Principle Machine Learning Engineer</t>
+          <t>EMEA Field CTO, DX — Engineering Executive Advisor</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1693,7 +1681,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27455</t>
+          <t>https://www.atlassian.com/company/careers/details/24899</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1715,7 +1703,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Principle Machine Learning Systems Engineer</t>
+          <t>AI Researcher, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1740,7 +1728,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27796</t>
+          <t>https://www.atlassian.com/company/careers/details/26246</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1762,12 +1750,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1775,7 +1763,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -1783,7 +1775,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26758</t>
+          <t>https://www.atlassian.com/company/careers/details/25539</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1805,12 +1797,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Principle Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1830,7 +1822,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25566</t>
+          <t>https://www.atlassian.com/company/careers/details/27455</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1852,12 +1844,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack (Loom Billing &amp; Integrations)</t>
+          <t>Principle Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1877,7 +1869,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27431</t>
+          <t>https://www.atlassian.com/company/careers/details/27796</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1899,12 +1891,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>AI Researcher (PhD), 2027 Graduate Canada</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1912,11 +1904,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
       <c r="F32" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -1924,7 +1912,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26074</t>
+          <t>https://www.atlassian.com/company/careers/details/26758</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1946,12 +1934,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer, 2027 Graduate U.S.</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1959,7 +1947,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -1967,7 +1959,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25997</t>
+          <t>https://www.atlassian.com/company/careers/details/25566</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -1989,12 +1981,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, 2027 Graduate Canada</t>
+          <t>Software Engineer – Full Stack (Loom Billing &amp; Integrations)</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2002,7 +1994,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -2010,7 +2006,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26070</t>
+          <t>https://www.atlassian.com/company/careers/details/27431</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2032,7 +2028,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, 2027 Graduate U.S.</t>
+          <t>AI Researcher (PhD), 2027 Graduate Canada</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2045,7 +2041,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25999</t>
+          <t>https://www.atlassian.com/company/careers/details/26074</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2075,12 +2075,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer, 2027 Graduate U.S</t>
+          <t>Security Engineer, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25998</t>
+          <t>https://www.atlassian.com/company/careers/details/25997</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, 2027 Graduate U.S.</t>
+          <t>Software Engineer, 2027 Graduate Canada</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25813</t>
+          <t>https://www.atlassian.com/company/careers/details/26070</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>AI Research Intern (PhD), 2027 Summer U.S.</t>
+          <t>Machine Learning Engineer, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2174,11 +2174,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -2186,7 +2182,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26269</t>
+          <t>https://www.atlassian.com/company/careers/details/25999</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2208,12 +2204,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, 2027 Canada</t>
+          <t>Data Engineer, 2027 Graduate U.S</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2229,7 +2225,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26275</t>
+          <t>https://www.atlassian.com/company/careers/details/25998</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2251,12 +2247,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer Intern, 2027 Summer U.S.</t>
+          <t>Software Engineer, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2264,11 +2260,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -2276,7 +2268,7 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26272</t>
+          <t>https://www.atlassian.com/company/careers/details/25813</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2298,12 +2290,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Research Intern, 2027 Summer U.S.</t>
+          <t>AI Research Intern (PhD), 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2311,7 +2303,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -2319,7 +2315,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26270</t>
+          <t>https://www.atlassian.com/company/careers/details/26269</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -2341,12 +2337,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Intern, 2027 Summer U.S.</t>
+          <t>Software Engineer Intern, 2027 Canada</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2362,7 +2358,7 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26268</t>
+          <t>https://www.atlassian.com/company/careers/details/26275</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -2384,12 +2380,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer Intern, 2027 Summer U.S.</t>
+          <t>Data Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2397,7 +2393,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26267</t>
+          <t>https://www.atlassian.com/company/careers/details/26272</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, 2027 Summer U.S.</t>
+          <t>Research Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26266</t>
+          <t>https://www.atlassian.com/company/careers/details/26270</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Product Design Intern, 2027 Summer U.S.</t>
+          <t>Machine Learning Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2483,11 +2483,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
       <c r="F45" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -2495,7 +2491,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26273</t>
+          <t>https://www.atlassian.com/company/careers/details/26268</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -2517,7 +2513,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Product Management Intern, 2027 Summer U.S.</t>
+          <t>Security Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2530,11 +2526,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
       <c r="F46" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -2542,7 +2534,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26274</t>
+          <t>https://www.atlassian.com/company/careers/details/26267</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -2564,7 +2556,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>AI Demand Intelligence Intern, 2027 Summer U.S.</t>
+          <t>Software Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2577,11 +2569,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
       <c r="F47" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -2589,7 +2577,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26843</t>
+          <t>https://www.atlassian.com/company/careers/details/26266</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -2611,12 +2599,12 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Enterprise Security Engineer</t>
+          <t>Product Design Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2636,7 +2624,7 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27275</t>
+          <t>https://www.atlassian.com/company/careers/details/26273</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -2658,12 +2646,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Enterprise Security Engineer</t>
+          <t>Product Management Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2683,7 +2671,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26986</t>
+          <t>https://www.atlassian.com/company/careers/details/26274</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -2705,12 +2693,12 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Security Testing Engineer - Penetration Tester</t>
+          <t>AI Demand Intelligence Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2720,7 +2708,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Remote or Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -2730,7 +2718,7 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26643</t>
+          <t>https://www.atlassian.com/company/careers/details/26843</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -2747,12 +2735,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Product Launch and price new features without waiting on engineering</t>
+          <t>Enterprise Security Engineer</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2765,7 +2753,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -2773,12 +2765,12 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/product/</t>
+          <t>https://www.atlassian.com/company/careers/details/27275</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -2790,12 +2782,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Growth Test offers, run promotions and lift conversion</t>
+          <t>Enterprise Security Engineer</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2808,7 +2800,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -2816,12 +2812,12 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/growth/</t>
+          <t>https://www.atlassian.com/company/careers/details/26986</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -2833,17 +2829,17 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
+          <t>Security Testing Engineer - Penetration Tester</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2853,7 +2849,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Remote or Remote</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2863,12 +2859,12 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
+          <t>https://www.atlassian.com/company/careers/details/26643</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -2880,12 +2876,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 3</t>
+          <t>Product Launch and price new features without waiting on engineering</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2898,11 +2894,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
       <c r="F54" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -2910,12 +2902,12 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer-3</t>
+          <t>https://www.chargebee.com/solutions/role/product/</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -2927,12 +2919,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer - 1</t>
+          <t>Growth Test offers, run promotions and lift conversion</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2945,11 +2937,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>India Full-time</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -2957,12 +2945,12 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://www.chargebee.com/solutions/role/growth/</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -2979,12 +2967,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2</t>
+          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2992,7 +2980,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>India Full-time</t>
+        </is>
+      </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -3000,7 +2992,7 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -3022,7 +3014,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer</t>
+          <t>Integration &amp; Customisation Engineer - 3</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3047,7 +3039,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-710627-implementation-engineer</t>
+          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer-3</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -3069,7 +3061,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Billing)</t>
+          <t>Integration &amp; Customization Engineer - 1</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3084,7 +3076,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -3094,7 +3086,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-700106-software-engineer-2-billing</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3116,7 +3108,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Voice)</t>
+          <t>Integration and Customisation Engineer - 2</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3129,11 +3121,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
       <c r="F59" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -3141,7 +3129,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3163,7 +3151,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Implementation Engineer</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -3188,7 +3176,7 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-710627-implementation-engineer</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -3210,7 +3198,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 3</t>
+          <t>Software Engineer - 2 (Billing)</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3235,7 +3223,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
+          <t>https://exotel.com/about-us/careers/#op-700106-software-engineer-2-billing</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -3257,7 +3245,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Software Engineer - 3 (Voice)</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -3282,7 +3270,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -3304,7 +3292,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3329,7 +3317,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -3351,12 +3339,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>Forward Deployed Engineer - 3</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3376,7 +3364,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -3393,12 +3381,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>CA Industrial Trainee</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -3411,7 +3399,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -3419,12 +3411,12 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Mumbai/CA-Industrial-Trainee_SR-46509-1</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3436,17 +3428,17 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer- WD</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3454,7 +3446,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -3462,12 +3458,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Full-Stack-Developer--WD_SR-45696-1</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3479,17 +3475,17 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-AWS</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3497,7 +3493,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Gen-AI-Engineer-AWS_SR-47131</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CPGR Growth Leader, AI Engineering, Strategic Accounts</t>
+          <t>CA Industrial Trainee</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-York/CPGR-Growth-Leader--AI-Engineering--Strategic-Accounts_SR-46966</t>
+          <t>https://fractal.ai/en-US/Careers/job/Mumbai/CA-Industrial-Trainee_SR-46509-1</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -3565,17 +3565,17 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Full Stack Developer- WD</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Full-Stack-Developer--WD_SR-45696-1</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3608,17 +3608,17 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Gen AI Engineer-AWS</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3634,12 +3634,12 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Gen-AI-Engineer-AWS_SR-47131</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -3651,17 +3651,17 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>CPGR Growth Leader, AI Engineering, Strategic Accounts</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3677,12 +3677,12 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-York/CPGR-Growth-Leader--AI-Engineering--Strategic-Accounts_SR-46966</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -3694,17 +3694,17 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3712,11 +3712,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru-VTP, India</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
       <c r="F72" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -3724,12 +3720,12 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -3741,17 +3737,17 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -3759,11 +3755,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>Hyderabad, Telangana, India</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
       <c r="F73" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -3771,12 +3763,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -3788,12 +3780,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3806,11 +3798,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>New Delhi, in</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
       <c r="F74" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -3818,12 +3806,12 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -3835,17 +3823,17 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3855,7 +3843,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Bengaluru-VTP, India</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -3865,12 +3853,12 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3882,17 +3870,17 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3900,7 +3888,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -3908,12 +3900,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3925,12 +3917,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -3943,7 +3935,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>New Delhi, in</t>
+        </is>
+      </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -3951,12 +3947,12 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -3968,17 +3964,17 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -3986,7 +3982,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr"/>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -3994,12 +3994,12 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -4011,17 +4011,17 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -4029,11 +4029,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
       <c r="F79" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -4041,12 +4037,12 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -4058,17 +4054,17 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -4084,12 +4080,12 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -4101,12 +4097,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Open Financial</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>We’re hiring Build with us Roles across engineering, product and GTM.</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -4127,12 +4123,12 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>https://open.money/company/careers</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>https://open.money/careers</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -4144,17 +4140,17 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -4162,7 +4158,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr"/>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -4170,12 +4170,12 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -4187,17 +4187,17 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Intern - Talent Acquisition</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -4205,11 +4205,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, Haryana</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="inlineStr"/>
       <c r="F83" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -4217,12 +4213,12 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -4234,17 +4230,17 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Open Financial</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>We’re hiring Build with us Roles across engineering, product and GTM.</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -4252,11 +4248,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -4264,12 +4256,12 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://open.money/company/careers</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://open.money/careers</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -4281,12 +4273,12 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -4299,11 +4291,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
       <c r="F85" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -4311,12 +4299,12 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -4333,7 +4321,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern</t>
+          <t>Intern - Talent Acquisition</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -4348,7 +4336,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Gurugram, Haryana</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -4358,7 +4346,7 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/6d7551f7-34c3-46a2-a4e4-18b29f15338c</t>
+          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -4380,7 +4368,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -4405,7 +4393,7 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -4427,7 +4415,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - IT Recruitment</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -4452,7 +4440,7 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/95eadc2b-27bf-40fe-b6e6-93aaeadd08f7</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -4469,17 +4457,17 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Talent Acquisition Intern</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -4487,7 +4475,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr"/>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -4495,12 +4487,12 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://jobs.lever.co/paytm/6d7551f7-34c3-46a2-a4e4-18b29f15338c</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
@@ -4512,17 +4504,17 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -4532,7 +4524,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -4542,12 +4534,12 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
@@ -4559,17 +4551,17 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Talent Acquisition Intern - IT Recruitment</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -4579,7 +4571,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -4589,12 +4581,12 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://jobs.lever.co/paytm/95eadc2b-27bf-40fe-b6e6-93aaeadd08f7</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -4606,17 +4598,17 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -4624,11 +4616,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
       <c r="F92" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -4636,12 +4624,12 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
@@ -4653,17 +4641,17 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -4671,7 +4659,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr"/>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -4679,12 +4671,12 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
@@ -4696,12 +4688,12 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>AI Builder</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -4716,7 +4708,7 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -4726,12 +4718,12 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4744950005</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
@@ -4743,17 +4735,17 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -4763,7 +4755,7 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -4773,12 +4765,12 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
@@ -4790,17 +4782,17 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Industrial Trainee</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -4808,11 +4800,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -4820,12 +4808,12 @@
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
@@ -4837,12 +4825,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Payroll Industrial Trainee</t>
+          <t>AI Builder</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -4857,7 +4845,7 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -4867,12 +4855,12 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8305308?gh_jid=8305308</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4744950005</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -4889,12 +4877,12 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -4904,7 +4892,7 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -4914,7 +4902,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -4936,7 +4924,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud: Azure</t>
+          <t>Industrial Trainee</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -4946,12 +4934,12 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>0-2 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bangalore </t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -4961,7 +4949,7 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -4983,7 +4971,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Payroll Industrial Trainee</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -4998,7 +4986,7 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
@@ -5008,7 +4996,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8305308?gh_jid=8305308</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -5025,17 +5013,17 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
+          <t xml:space="preserve">Security Engineer - Identity and Access </t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -5043,7 +5031,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr"/>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, India</t>
+        </is>
+      </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -5051,12 +5043,12 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzgsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
@@ -5068,12 +5060,12 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>AI Screenplay Writer</t>
+          <t>Software Engineer - Cloud: Azure</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -5083,10 +5075,14 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr"/>
+          <t>0-2 years</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bangalore </t>
+        </is>
+      </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -5094,12 +5090,12 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
@@ -5111,12 +5107,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>AI Video Editor</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -5129,7 +5125,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr"/>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -5137,12 +5137,12 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
@@ -5159,12 +5159,12 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>AI Sound Designer</t>
+          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzgsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>AI Screenplay Writer</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -5240,17 +5240,17 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>AI Video Editor</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -5258,11 +5258,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E106" s="4" t="inlineStr"/>
       <c r="F106" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -5270,12 +5266,12 @@
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
@@ -5287,17 +5283,17 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>AI Sound Designer</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -5305,11 +5301,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E107" s="4" t="inlineStr"/>
       <c r="F107" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -5317,12 +5309,12 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
@@ -5334,17 +5326,17 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>SirionLabs</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Intern- Employee Engagement</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -5360,12 +5352,12 @@
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>https://www.sirionlabs.com/careers/</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
@@ -5377,17 +5369,17 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -5395,7 +5387,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr"/>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -5403,12 +5399,12 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
@@ -5420,17 +5416,17 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -5440,7 +5436,7 @@
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
@@ -5450,12 +5446,12 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
@@ -5467,29 +5463,25 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>SirionLabs</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, New Grad</t>
+          <t>Intern- Employee Engagement</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>new grad</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr"/>
       <c r="F111" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -5497,12 +5489,12 @@
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8130876</t>
+          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://www.sirionlabs.com/careers/</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
@@ -5514,17 +5506,17 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -5532,11 +5524,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
       <c r="F112" s="4" t="inlineStr">
         <is>
           <t>2026-10-28</t>
@@ -5544,12 +5532,12 @@
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
@@ -5561,17 +5549,17 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -5581,7 +5569,7 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
@@ -5591,12 +5579,12 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
@@ -5608,52 +5596,193 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
+          <t>Stripe India</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, New Grad</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>new grad</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8130876</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/stripe</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Test Jerin</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
           <t>Zscaler India</t>
         </is>
       </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>Escalation Engineer</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>Software (General)</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E114" s="4" t="inlineStr">
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
         <is>
           <t>Bangalore, IND</t>
         </is>
       </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="G114" s="5" t="inlineStr">
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/zscaler/jobs/5263563007</t>
         </is>
       </c>
-      <c r="H114" s="4" t="inlineStr">
+      <c r="H117" s="4" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/zscaler</t>
         </is>
       </c>
-      <c r="I114" s="4" t="inlineStr">
+      <c r="I117" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I114"/>
+  <autoFilter ref="A1:I117"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -5768,6 +5897,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId116"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5779,7 +5911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5847,35 +5979,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Plivo</t>
+          <t>Log9 Materials</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.plivo.com/careers/</t>
+          <t>https://www.log9materials.com/careers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.plivo.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Log9 Materials</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://www.log9materials.com/careers</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5884,18 +5996,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5904,38 +6016,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Tonbo Imaging</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://www.tonboimaging.com/careers/</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.tonboimaging.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5944,18 +6036,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Blinkit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://blinkit.com/careers</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5964,18 +6056,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>CRED</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://careers.cred.club/</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5984,18 +6076,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Capillary Technologies</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://www.capillarytech.com/careers/</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6004,18 +6096,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Cleartrip</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://www.cleartrip.com/careers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6024,18 +6116,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -6044,18 +6136,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6064,18 +6156,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6084,58 +6176,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Netcore Cloud</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>https://netcorecloud.com/careers/</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://netcorecloud.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>OYO</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>https://www.oyorooms.com/careers/</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.oyorooms.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -6144,38 +6196,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Shiprocket</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>https://www.shiprocket.in/careers/</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.shiprocket.in/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Swiggy</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://careers.swiggy.com/</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6184,18 +6216,18 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -6204,18 +6236,18 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -6224,18 +6256,18 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6244,18 +6276,18 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Mastek</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>https://www.mastek.com/careers</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
